--- a/docs/Files/Small-format_model/ODYM_T6_LifetimeSF_V1.0.xlsx
+++ b/docs/Files/Small-format_model/ODYM_T6_LifetimeSF_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE91B247-6245-4454-AC91-A9B210ECCDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80E4AA0-F930-42A7-BD0E-576DC2BE2E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="1290" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -309,15 +309,6 @@
     <t>notes</t>
   </si>
   <si>
-    <t>EV LIB</t>
-  </si>
-  <si>
-    <t>other EV LIB products</t>
-  </si>
-  <si>
-    <t>3;12;5.0;none</t>
-  </si>
-  <si>
     <t>assuming 12yrs for now</t>
   </si>
   <si>
@@ -328,6 +319,15 @@
   </si>
   <si>
     <t>ODYM_Classifications_SF</t>
+  </si>
+  <si>
+    <t>SF LIB</t>
+  </si>
+  <si>
+    <t>other SF LIB products</t>
+  </si>
+  <si>
+    <t>1;3;2.0;none</t>
   </si>
 </sst>
 </file>
@@ -790,7 +790,7 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>18</v>
@@ -804,7 +804,7 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>18</v>
@@ -874,7 +874,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>18</v>
@@ -958,7 +958,7 @@
         <v>39</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>18</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1166,18 +1166,18 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1186,10 +1186,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Files/Small-format_model/ODYM_T6_LifetimeSF_V1.0.xlsx
+++ b/docs/Files/Small-format_model/ODYM_T6_LifetimeSF_V1.0.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80E4AA0-F930-42A7-BD0E-576DC2BE2E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8EE87B-F7CC-446E-981D-1176548A46E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -327,7 +327,7 @@
     <t>other SF LIB products</t>
   </si>
   <si>
-    <t>1;3;2.0;none</t>
+    <t>3;2;1.0;none</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1157,7 @@
         <v>96</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1177,7 +1177,7 @@
         <v>97</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
